--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260701.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>12,900,000</t>
+          <t>12,800,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.03%</t>
+          <t>18.39%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.15%</t>
+          <t>7.27%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.64%</t>
+          <t>6.57%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>5.34%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>3,380,000</t>
+          <t>3,450,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>5.18%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>4.23%</t>
         </is>
       </c>
     </row>
@@ -743,56 +743,56 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>1,140,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,435,000</t>
+          <t>940,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.61%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>940,000</t>
+          <t>1,435,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.32%</t>
+          <t>3.57%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>6,440,000</t>
+          <t>790,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>790,000</t>
+          <t>6,440,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>5,300,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>3,217,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>3,217,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1056,183 +1056,183 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>9,911,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>279,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>279,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>10,000,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>10,000,000</t>
+          <t>7,550,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>7,550,000</t>
+          <t>1,950,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,950,000</t>
+          <t>390,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>390,000</t>
+          <t>5,500,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1298,24 +1298,24 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,88 +1327,88 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>3,500,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>3,500,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1623,24 +1623,24 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,358,718,385</t>
+          <t>5,929,354,917</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,484,118,663</t>
+          <t>1,748,522,183</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
